--- a/data/trans_dic/P38A-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P38A-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a</t>
+          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,03; 89,95</t>
+          <t>84,79; 90,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,38; 87,71</t>
+          <t>82,27; 87,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,9; 92,35</t>
+          <t>84,41; 92,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86,39; 91,23</t>
+          <t>86,42; 91,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,22; 91,92</t>
+          <t>87,25; 91,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,63; 94,52</t>
+          <t>90,85; 94,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,54; 89,99</t>
+          <t>86,49; 89,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85,51; 89,26</t>
+          <t>85,49; 89,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>88,95; 92,93</t>
+          <t>88,91; 92,93</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>80,56; 85,61</t>
+          <t>80,79; 85,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,13; 85,16</t>
+          <t>80,15; 85,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,5; 83,56</t>
+          <t>32,36; 83,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,13; 90,39</t>
+          <t>86,2; 90,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,3; 93,64</t>
+          <t>90,6; 93,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,44; 90,31</t>
+          <t>86,27; 90,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,15; 87,26</t>
+          <t>84,18; 87,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>85,86; 89,06</t>
+          <t>85,95; 88,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,41; 86,3</t>
+          <t>51,44; 86,1</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,38; 87,87</t>
+          <t>82,65; 87,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80,43; 86,28</t>
+          <t>80,4; 85,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,9; 86,88</t>
+          <t>78,74; 87,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,79; 92,23</t>
+          <t>88,06; 92,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89,17; 93,27</t>
+          <t>89,16; 93,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,13; 95,94</t>
+          <t>89,31; 96,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,91; 89,39</t>
+          <t>85,91; 89,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85,73; 89,07</t>
+          <t>85,6; 89,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85,86; 92,35</t>
+          <t>85,94; 92,7</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,57; 87,81</t>
+          <t>83,41; 87,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,1; 85,84</t>
+          <t>80,81; 85,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,81; 83,73</t>
+          <t>76,55; 83,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89,07; 92,61</t>
+          <t>89,24; 92,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,41; 88,83</t>
+          <t>84,21; 88,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,52; 87,65</t>
+          <t>64,88; 87,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,03; 89,87</t>
+          <t>87,23; 90,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,3; 86,53</t>
+          <t>83,31; 86,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,45; 84,63</t>
+          <t>70,98; 84,59</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>83,91; 86,39</t>
+          <t>84,06; 86,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,19; 84,76</t>
+          <t>82,27; 84,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60,45; 84,15</t>
+          <t>60,3; 84,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88,5; 90,61</t>
+          <t>88,7; 90,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>88,79; 90,81</t>
+          <t>88,86; 90,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,85; 90,51</t>
+          <t>82,43; 90,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,69; 88,34</t>
+          <t>86,75; 88,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,96; 87,58</t>
+          <t>85,97; 87,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73,87; 86,85</t>
+          <t>72,82; 86,61</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a</t>
+          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>595433; 629884</t>
+          <t>593775; 630667</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>552664; 588448</t>
+          <t>551960; 587774</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>539493; 586825</t>
+          <t>536360; 586141</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>600484; 634068</t>
+          <t>600694; 633391</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>585302; 616844</t>
+          <t>585506; 615177</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>612089; 638329</t>
+          <t>613588; 639348</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1207546; 1255676</t>
+          <t>1206828; 1254756</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1147607; 1197913</t>
+          <t>1147254; 1196909</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1165917; 1218200</t>
+          <t>1165450; 1218152</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>814229; 865254</t>
+          <t>816526; 866255</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>814362; 865496</t>
+          <t>814519; 864717</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>435398; 996726</t>
+          <t>386057; 996432</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>887306; 931238</t>
+          <t>888028; 929900</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>939043; 973787</t>
+          <t>942128; 974293</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>828189; 865307</t>
+          <t>826569; 864403</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1717395; 1781011</t>
+          <t>1718042; 1784363</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1765352; 1831156</t>
+          <t>1767384; 1828128</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1105712; 1856380</t>
+          <t>1106526; 1851972</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>619331; 660658</t>
+          <t>621371; 661288</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>603150; 647063</t>
+          <t>602924; 644186</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>555972; 612255</t>
+          <t>554856; 613657</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>678082; 712384</t>
+          <t>680227; 713917</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>699167; 731346</t>
+          <t>699055; 731510</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>831917; 895426</t>
+          <t>833621; 898274</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1309447; 1362599</t>
+          <t>1309458; 1363029</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1315145; 1366390</t>
+          <t>1313140; 1367442</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1406468; 1512664</t>
+          <t>1407806; 1518432</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>785994; 825873</t>
+          <t>784554; 826911</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>756317; 800557</t>
+          <t>753645; 798158</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>711854; 776016</t>
+          <t>709515; 770810</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>932606; 969668</t>
+          <t>934387; 970624</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>877491; 923440</t>
+          <t>875364; 920972</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>706452; 959729</t>
+          <t>710352; 961943</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1729790; 1786257</t>
+          <t>1733775; 1789256</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1642715; 1706469</t>
+          <t>1642905; 1706184</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1404030; 1711111</t>
+          <t>1435146; 1710175</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2855711; 2940312</t>
+          <t>2860774; 2942933</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2769411; 2856110</t>
+          <t>2772382; 2859762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2091288; 2911284</t>
+          <t>2086175; 2907628</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3136959; 3211722</t>
+          <t>3144175; 3214748</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3138530; 3209704</t>
+          <t>3141000; 3213062</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2997333; 3314381</t>
+          <t>3018496; 3318496</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6023651; 6137725</t>
+          <t>6027244; 6135003</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5934921; 6046536</t>
+          <t>5935473; 6046855</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5260639; 6184803</t>
+          <t>5186081; 6167817</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38A-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P38A-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,79; 90,06</t>
+          <t>84,72; 89,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,27; 87,61</t>
+          <t>82,29; 87,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,41; 92,24</t>
+          <t>85,68; 91,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86,42; 91,13</t>
+          <t>86,04; 90,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,25; 91,67</t>
+          <t>87,16; 91,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,85; 94,67</t>
+          <t>89,69; 93,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,49; 89,92</t>
+          <t>86,68; 90,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85,49; 89,19</t>
+          <t>85,58; 89,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>88,91; 92,93</t>
+          <t>88,5; 92,38</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>84,81%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>80,79; 85,71</t>
+          <t>80,69; 85,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,15; 85,09</t>
+          <t>79,92; 84,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,36; 83,53</t>
+          <t>78,78; 84,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,2; 90,26</t>
+          <t>86,07; 90,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,6; 93,69</t>
+          <t>90,42; 93,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,27; 90,22</t>
+          <t>85,6; 89,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,18; 87,43</t>
+          <t>84,23; 87,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>85,95; 88,91</t>
+          <t>85,94; 88,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,44; 86,1</t>
+          <t>83,02; 86,54</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,65; 87,96</t>
+          <t>82,19; 87,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80,4; 85,9</t>
+          <t>80,75; 86,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,74; 87,08</t>
+          <t>78,66; 86,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88,06; 92,42</t>
+          <t>87,93; 92,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89,16; 93,3</t>
+          <t>89,08; 93,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,31; 96,24</t>
+          <t>87,85; 92,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,91; 89,42</t>
+          <t>85,83; 89,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85,6; 89,14</t>
+          <t>85,84; 89,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85,94; 92,7</t>
+          <t>84,27; 88,65</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>82,47%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,41; 87,92</t>
+          <t>83,63; 88,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80,81; 85,59</t>
+          <t>80,79; 85,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,55; 83,17</t>
+          <t>75,49; 82,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89,24; 92,7</t>
+          <t>89,22; 92,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,21; 88,59</t>
+          <t>84,37; 88,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,88; 87,85</t>
+          <t>82,99; 87,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,23; 90,02</t>
+          <t>87,04; 89,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,31; 86,51</t>
+          <t>83,35; 86,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70,98; 84,59</t>
+          <t>80,4; 84,38</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>84,06; 86,47</t>
+          <t>84,02; 86,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,27; 84,87</t>
+          <t>82,1; 84,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60,3; 84,04</t>
+          <t>80,98; 84,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88,7; 90,69</t>
+          <t>88,57; 90,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>88,86; 90,9</t>
+          <t>88,75; 90,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,43; 90,63</t>
+          <t>87,33; 89,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,75; 88,3</t>
+          <t>86,67; 88,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,97; 87,58</t>
+          <t>85,91; 87,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>72,82; 86,61</t>
+          <t>84,7; 86,58</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>569771</t>
+          <t>615437</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>626872</t>
+          <t>673401</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1196644</t>
+          <t>1288837</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>593775; 630667</t>
+          <t>593317; 629309</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>551960; 587774</t>
+          <t>552061; 589612</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>536360; 586141</t>
+          <t>591786; 635364</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>600694; 633391</t>
+          <t>598027; 631668</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>585506; 615177</t>
+          <t>584907; 616105</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>613588; 639348</t>
+          <t>657162; 687075</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1206828; 1254756</t>
+          <t>1209422; 1256024</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1147254; 1196909</t>
+          <t>1148425; 1196413</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1165450; 1218152</t>
+          <t>1259743; 1315019</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>783342</t>
+          <t>857747</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>847716</t>
+          <t>940001</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1631059</t>
+          <t>1797748</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>816526; 866255</t>
+          <t>815565; 866931</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>814519; 864717</t>
+          <t>812232; 862233</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>386057; 996432</t>
+          <t>826324; 885910</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>888028; 929900</t>
+          <t>886734; 929605</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>942128; 974293</t>
+          <t>940255; 973486</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>826569; 864403</t>
+          <t>916641; 961259</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1718042; 1784363</t>
+          <t>1719031; 1782220</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1767384; 1828128</t>
+          <t>1767098; 1829836</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1106526; 1851972</t>
+          <t>1759815; 1834487</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>588628</t>
+          <t>665706</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>863233</t>
+          <t>733368</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1451862</t>
+          <t>1399074</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>621371; 661288</t>
+          <t>617905; 659890</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>602924; 644186</t>
+          <t>605554; 646618</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>554856; 613657</t>
+          <t>631667; 692209</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>680227; 713917</t>
+          <t>679216; 712641</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>699055; 731510</t>
+          <t>698483; 730539</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>833621; 898274</t>
+          <t>713586; 750138</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1309458; 1363029</t>
+          <t>1308196; 1362614</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1313140; 1367442</t>
+          <t>1316790; 1367778</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1407806; 1518432</t>
+          <t>1361321; 1432040</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>744797</t>
+          <t>781778</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>893143</t>
+          <t>957613</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1637940</t>
+          <t>1739391</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>784554; 826911</t>
+          <t>786545; 827765</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>753645; 798158</t>
+          <t>753415; 800291</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>709515; 770810</t>
+          <t>747418; 812657</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>934387; 970624</t>
+          <t>934162; 970866</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>875364; 920972</t>
+          <t>877079; 921335</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>710352; 961943</t>
+          <t>928651; 980020</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1733775; 1789256</t>
+          <t>1729978; 1787580</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1642905; 1706184</t>
+          <t>1643745; 1707954</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1435146; 1710175</t>
+          <t>1695706; 1779724</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2686540</t>
+          <t>2920668</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3230964</t>
+          <t>3304382</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5917504</t>
+          <t>6225050</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2860774; 2942933</t>
+          <t>2859498; 2945380</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2772382; 2859762</t>
+          <t>2766571; 2861634</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2086175; 2907628</t>
+          <t>2860688; 2978934</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3144175; 3214748</t>
+          <t>3139531; 3211973</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3141000; 3213062</t>
+          <t>3136841; 3209728</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3018496; 3318496</t>
+          <t>3261548; 3344085</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6027244; 6135003</t>
+          <t>6022229; 6135304</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5935473; 6046855</t>
+          <t>5931871; 6042142</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5186081; 6167817</t>
+          <t>6155819; 6292662</t>
         </is>
       </c>
     </row>
